--- a/Script Outputs.xlsx
+++ b/Script Outputs.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annaelleman/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annaelleman/Desktop/SwellPaper/Scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103FA9F6-7EE5-3C4A-9D89-A6E816268D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{923B5BAF-A668-E642-BD56-F3655A116CAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="2200" windowWidth="28040" windowHeight="17440" activeTab="2" xr2:uid="{04CA3191-F1AA-D241-8537-5E86D3BF4C26}"/>
+    <workbookView xWindow="8580" yWindow="760" windowWidth="28040" windowHeight="17440" activeTab="3" xr2:uid="{04CA3191-F1AA-D241-8537-5E86D3BF4C26}"/>
   </bookViews>
   <sheets>
     <sheet name="membrane and cell workups" sheetId="1" r:id="rId1"/>
     <sheet name="patch workup" sheetId="2" r:id="rId2"/>
     <sheet name="poke workup" sheetId="3" r:id="rId3"/>
+    <sheet name="pull workup" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="143">
   <si>
     <t>filename</t>
   </si>
@@ -458,6 +459,18 @@
   </si>
   <si>
     <t>no user inputs are required for this script--everything is hard coded</t>
+  </si>
+  <si>
+    <t>rows for radii workup can be chosen by brightness (see instructions in line 232)</t>
+  </si>
+  <si>
+    <t>user inputs can be omitted from this workup if desired (line 230)</t>
+  </si>
+  <si>
+    <t>Membrane Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">radius of solution, see https://pypi.org/project/circle-fit/ </t>
   </si>
 </sst>
 </file>
@@ -1503,4 +1516,158 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6A1AE52-883A-614A-9340-F4031B74053F}">
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="70.33203125" customWidth="1"/>
+    <col min="5" max="5" width="79" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>141</v>
+      </c>
+      <c r="B8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>